--- a/m3-obec-study-form.xlsx
+++ b/m3-obec-study-form.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dmc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9169F9F-5343-4677-B8E9-34730D104F53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA78F9C0-BA44-4913-A025-493810DC9F08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4155" yWindow="2370" windowWidth="21735" windowHeight="11295" xr2:uid="{CF76439A-2838-42B1-AF09-5DD6D3883603}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CF76439A-2838-42B1-AF09-5DD6D3883603}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,21 +36,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="881" uniqueCount="414">
-  <si>
-    <t>นาย</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="875" uniqueCount="410">
   <si>
     <t>(ม.3) ศึกษาต่อ ม.4 โรงเรียนเดิม</t>
-  </si>
-  <si>
-    <t>นางสาว</t>
-  </si>
-  <si>
-    <t>ดนุพงศ์  ย่องดำ</t>
-  </si>
-  <si>
-    <t>อภิสรา  ธรรมชีพ</t>
   </si>
   <si>
     <t>ลำดับ</t>
@@ -1715,7 +1703,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1BACD4A-4E8F-42F5-B18A-2D02AA676E1B}">
-  <dimension ref="A1:G220"/>
+  <dimension ref="A1:G218"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="12.85546875" customWidth="1"/>
@@ -1726,25 +1714,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="F1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="G1" s="6" t="s">
         <v>7</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -1752,20 +1740,20 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="1">
         <v>18551</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -1773,20 +1761,20 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="1">
         <v>18570</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -1794,20 +1782,20 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="1">
         <v>18573</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -1815,20 +1803,20 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="1">
         <v>18577</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -1836,20 +1824,20 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="1">
         <v>18579</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -1857,20 +1845,20 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="1">
         <v>18587</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -1878,20 +1866,20 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="1">
         <v>18591</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -1899,20 +1887,20 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="1">
         <v>18592</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -1920,20 +1908,20 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="1">
         <v>18595</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -1941,20 +1929,20 @@
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="1">
         <v>18598</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -1962,20 +1950,20 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="1">
         <v>18599</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -1983,20 +1971,20 @@
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C13" s="4"/>
       <c r="D13" s="1">
         <v>18602</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -2004,20 +1992,20 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C14" s="4"/>
       <c r="D14" s="1">
         <v>18605</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -2025,20 +2013,20 @@
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="1">
         <v>18606</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -2046,20 +2034,20 @@
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="1">
         <v>18607</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -2067,20 +2055,20 @@
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C17" s="4"/>
       <c r="D17" s="1">
         <v>18624</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -2088,20 +2076,20 @@
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C18" s="4"/>
       <c r="D18" s="1">
         <v>18639</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -2109,20 +2097,20 @@
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C19" s="4"/>
       <c r="D19" s="1">
         <v>18642</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -2130,20 +2118,20 @@
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C20" s="4"/>
       <c r="D20" s="1">
         <v>18647</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -2151,20 +2139,20 @@
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C21" s="4"/>
       <c r="D21" s="1">
         <v>18653</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -2172,20 +2160,20 @@
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C22" s="4"/>
       <c r="D22" s="1">
         <v>18656</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -2193,20 +2181,20 @@
         <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C23" s="4"/>
       <c r="D23" s="1">
         <v>18667</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -2214,20 +2202,20 @@
         <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C24" s="4"/>
       <c r="D24" s="1">
         <v>18679</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -2235,20 +2223,20 @@
         <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C25" s="4"/>
       <c r="D25" s="1">
         <v>18783</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -2256,20 +2244,20 @@
         <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C26" s="4"/>
       <c r="D26" s="1">
         <v>18785</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -2277,20 +2265,20 @@
         <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C27" s="4"/>
       <c r="D27" s="1">
         <v>18811</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -2298,20 +2286,20 @@
         <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C28" s="4"/>
       <c r="D28" s="1">
         <v>18853</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -2319,20 +2307,20 @@
         <v>28</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C29" s="4"/>
       <c r="D29" s="1">
         <v>18875</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -2340,20 +2328,20 @@
         <v>29</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C30" s="4"/>
       <c r="D30" s="1">
         <v>18878</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -2361,20 +2349,20 @@
         <v>30</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C31" s="4"/>
       <c r="D31" s="1">
         <v>18574</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -2382,20 +2370,20 @@
         <v>31</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C32" s="4"/>
       <c r="D32" s="1">
         <v>18584</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -2403,20 +2391,20 @@
         <v>32</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C33" s="4"/>
       <c r="D33" s="1">
         <v>18590</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -2424,20 +2412,20 @@
         <v>33</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C34" s="4"/>
       <c r="D34" s="1">
         <v>18601</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -2445,20 +2433,20 @@
         <v>34</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C35" s="4"/>
       <c r="D35" s="1">
         <v>18615</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -2466,20 +2454,20 @@
         <v>35</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C36" s="4"/>
       <c r="D36" s="1">
         <v>18632</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -2487,20 +2475,20 @@
         <v>36</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C37" s="4"/>
       <c r="D37" s="1">
         <v>18651</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -2508,20 +2496,20 @@
         <v>37</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C38" s="4"/>
       <c r="D38" s="1">
         <v>18660</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -2529,20 +2517,20 @@
         <v>38</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C39" s="4"/>
       <c r="D39" s="1">
         <v>18664</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -2550,20 +2538,20 @@
         <v>39</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C40" s="4"/>
       <c r="D40" s="1">
         <v>18665</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -2571,20 +2559,20 @@
         <v>40</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C41" s="4"/>
       <c r="D41" s="1">
         <v>18687</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -2592,20 +2580,20 @@
         <v>41</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C42" s="4"/>
       <c r="D42" s="1">
         <v>18695</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -2613,20 +2601,20 @@
         <v>42</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C43" s="4"/>
       <c r="D43" s="1">
         <v>18700</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -2634,20 +2622,20 @@
         <v>43</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C44" s="3"/>
       <c r="D44" s="1">
         <v>18725</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -2655,20 +2643,20 @@
         <v>44</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C45" s="7"/>
       <c r="D45" s="1">
         <v>18728</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -2676,20 +2664,20 @@
         <v>45</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C46" s="8"/>
       <c r="D46" s="1">
         <v>18806</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -2697,20 +2685,20 @@
         <v>46</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C47" s="8"/>
       <c r="D47" s="1">
         <v>18818</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -2718,20 +2706,20 @@
         <v>47</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C48" s="8"/>
       <c r="D48" s="1">
         <v>18820</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -2739,20 +2727,20 @@
         <v>48</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C49" s="8"/>
       <c r="D49" s="1">
         <v>18850</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -2760,20 +2748,20 @@
         <v>49</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C50" s="8"/>
       <c r="D50" s="1">
         <v>18876</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -2781,20 +2769,20 @@
         <v>50</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C51" s="8"/>
       <c r="D51" s="1">
         <v>19444</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -2802,20 +2790,20 @@
         <v>51</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C52" s="8"/>
       <c r="D52" s="1">
         <v>19492</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -2823,20 +2811,20 @@
         <v>52</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C53" s="8"/>
       <c r="D53" s="1">
         <v>18539</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -2844,20 +2832,20 @@
         <v>53</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C54" s="8"/>
       <c r="D54" s="1">
         <v>18562</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -2865,20 +2853,20 @@
         <v>54</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C55" s="8"/>
       <c r="D55" s="1">
         <v>18611</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -2886,20 +2874,20 @@
         <v>55</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C56" s="8"/>
       <c r="D56" s="1">
         <v>18617</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -2907,20 +2895,20 @@
         <v>56</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C57" s="8"/>
       <c r="D57" s="1">
         <v>18626</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -2928,20 +2916,20 @@
         <v>57</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C58" s="8"/>
       <c r="D58" s="1">
         <v>18627</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -2949,20 +2937,20 @@
         <v>58</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C59" s="8"/>
       <c r="D59" s="1">
         <v>18629</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -2970,20 +2958,20 @@
         <v>59</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C60" s="8"/>
       <c r="D60" s="1">
         <v>18630</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -2991,20 +2979,20 @@
         <v>60</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C61" s="8"/>
       <c r="D61" s="1">
         <v>18634</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -3012,20 +3000,20 @@
         <v>61</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C62" s="8"/>
       <c r="D62" s="1">
         <v>18652</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -3033,20 +3021,20 @@
         <v>62</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C63" s="8"/>
       <c r="D63" s="1">
         <v>18654</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -3054,20 +3042,20 @@
         <v>63</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C64" s="8"/>
       <c r="D64" s="1">
         <v>18655</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -3075,20 +3063,20 @@
         <v>64</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C65" s="8"/>
       <c r="D65" s="1">
         <v>18675</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -3096,20 +3084,20 @@
         <v>65</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C66" s="8"/>
       <c r="D66" s="1">
         <v>18677</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="G66" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -3117,20 +3105,20 @@
         <v>66</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C67" s="8"/>
       <c r="D67" s="1">
         <v>18681</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G67" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -3138,20 +3126,20 @@
         <v>67</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C68" s="8"/>
       <c r="D68" s="1">
         <v>18705</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="G68" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -3159,20 +3147,20 @@
         <v>68</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C69" s="8"/>
       <c r="D69" s="1">
         <v>18714</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="G69" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -3180,20 +3168,20 @@
         <v>69</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C70" s="8"/>
       <c r="D70" s="1">
         <v>18737</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="G70" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -3201,20 +3189,20 @@
         <v>70</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C71" s="8"/>
       <c r="D71" s="1">
         <v>18744</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="G71" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -3222,20 +3210,20 @@
         <v>71</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C72" s="8"/>
       <c r="D72" s="1">
         <v>18745</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="G72" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -3243,20 +3231,20 @@
         <v>72</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C73" s="8"/>
       <c r="D73" s="1">
         <v>18754</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -3264,20 +3252,20 @@
         <v>73</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C74" s="8"/>
       <c r="D74" s="1">
         <v>18789</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="G74" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -3285,20 +3273,20 @@
         <v>74</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C75" s="8"/>
       <c r="D75" s="1">
         <v>18799</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="G75" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -3306,20 +3294,20 @@
         <v>75</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C76" s="8"/>
       <c r="D76" s="1">
         <v>18800</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="G76" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -3327,20 +3315,20 @@
         <v>76</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C77" s="8"/>
       <c r="D77" s="1">
         <v>18834</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="G77" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -3348,20 +3336,20 @@
         <v>77</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C78" s="8"/>
       <c r="D78" s="1">
         <v>18859</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G78" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -3369,20 +3357,20 @@
         <v>78</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C79" s="8"/>
       <c r="D79" s="1">
         <v>18869</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="G79" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -3390,20 +3378,20 @@
         <v>79</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C80" s="8"/>
       <c r="D80" s="1">
         <v>18870</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="G80" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -3411,20 +3399,20 @@
         <v>80</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C81" s="8"/>
       <c r="D81" s="1">
         <v>19422</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -3432,20 +3420,20 @@
         <v>81</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C82" s="8"/>
       <c r="D82" s="1">
         <v>19927</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="G82" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -3453,20 +3441,20 @@
         <v>82</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C83" s="8"/>
       <c r="D83" s="1">
         <v>18230</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="G83" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -3474,20 +3462,20 @@
         <v>83</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C84" s="8"/>
       <c r="D84" s="1">
         <v>18242</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="G84" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -3495,20 +3483,20 @@
         <v>84</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C85" s="8"/>
       <c r="D85" s="1">
         <v>18393</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="G85" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -3516,20 +3504,20 @@
         <v>85</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C86" s="8"/>
       <c r="D86" s="1">
         <v>18394</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="G86" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -3537,20 +3525,20 @@
         <v>86</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C87" s="8"/>
       <c r="D87" s="1">
         <v>18402</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="G87" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -3558,20 +3546,20 @@
         <v>87</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C88" s="8"/>
       <c r="D88" s="1">
         <v>18553</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G88" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -3579,20 +3567,20 @@
         <v>88</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C89" s="8"/>
       <c r="D89" s="1">
         <v>18578</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="G89" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -3600,20 +3588,20 @@
         <v>89</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C90" s="8"/>
       <c r="D90" s="1">
         <v>18631</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="G90" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -3621,20 +3609,20 @@
         <v>90</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C91" s="8"/>
       <c r="D91" s="1">
         <v>18657</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="G91" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -3642,20 +3630,20 @@
         <v>91</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C92" s="8"/>
       <c r="D92" s="1">
         <v>18666</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="G92" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -3663,20 +3651,20 @@
         <v>92</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C93" s="8"/>
       <c r="D93" s="1">
         <v>18707</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="G93" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -3684,20 +3672,20 @@
         <v>93</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C94" s="8"/>
       <c r="D94" s="1">
         <v>18709</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="G94" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -3705,20 +3693,20 @@
         <v>94</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C95" s="8"/>
       <c r="D95" s="1">
         <v>18713</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="G95" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -3726,20 +3714,20 @@
         <v>95</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C96" s="8"/>
       <c r="D96" s="1">
         <v>18717</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="G96" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -3747,20 +3735,20 @@
         <v>96</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C97" s="8"/>
       <c r="D97" s="1">
         <v>18720</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="G97" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -3768,20 +3756,20 @@
         <v>97</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C98" s="8"/>
       <c r="D98" s="1">
         <v>18721</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="G98" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -3789,20 +3777,20 @@
         <v>98</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C99" s="8"/>
       <c r="D99" s="1">
         <v>18740</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="G99" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -3810,20 +3798,20 @@
         <v>99</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C100" s="8"/>
       <c r="D100" s="1">
         <v>18749</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="G100" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -3831,20 +3819,20 @@
         <v>100</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C101" s="8"/>
       <c r="D101" s="1">
         <v>18761</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="G101" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -3852,20 +3840,20 @@
         <v>101</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C102" s="8"/>
       <c r="D102" s="1">
         <v>18765</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="G102" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -3873,20 +3861,20 @@
         <v>102</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C103" s="8"/>
       <c r="D103" s="1">
         <v>18767</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="G103" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -3894,20 +3882,20 @@
         <v>103</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C104" s="8"/>
       <c r="D104" s="1">
         <v>18769</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="G104" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -3915,20 +3903,20 @@
         <v>104</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C105" s="8"/>
       <c r="D105" s="1">
         <v>18784</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="G105" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -3936,20 +3924,20 @@
         <v>105</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C106" s="8"/>
       <c r="D106" s="1">
         <v>18788</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="G106" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -3957,20 +3945,20 @@
         <v>106</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C107" s="8"/>
       <c r="D107" s="1">
         <v>18845</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="G107" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -3978,20 +3966,20 @@
         <v>107</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C108" s="8"/>
       <c r="D108" s="1">
         <v>18851</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="G108" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -3999,20 +3987,20 @@
         <v>108</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C109" s="8"/>
       <c r="D109" s="1">
         <v>18872</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="G109" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -4020,20 +4008,20 @@
         <v>109</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C110" s="8"/>
       <c r="D110" s="1">
         <v>18884</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="G110" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -4041,20 +4029,20 @@
         <v>110</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C111" s="8"/>
       <c r="D111" s="1">
         <v>19901</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="F111" s="3" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="G111" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -4062,20 +4050,20 @@
         <v>111</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C112" s="8"/>
       <c r="D112" s="1">
         <v>18540</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="G112" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -4083,20 +4071,20 @@
         <v>112</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C113" s="8"/>
       <c r="D113" s="1">
         <v>18549</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="F113" s="3" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="G113" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -4104,20 +4092,20 @@
         <v>113</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C114" s="8"/>
       <c r="D114" s="1">
         <v>18568</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G114" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -4125,20 +4113,20 @@
         <v>114</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C115" s="8"/>
       <c r="D115" s="1">
         <v>18589</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="G115" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -4146,20 +4134,20 @@
         <v>115</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C116" s="8"/>
       <c r="D116" s="1">
         <v>18594</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="G116" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -4167,20 +4155,20 @@
         <v>116</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C117" s="8"/>
       <c r="D117" s="1">
         <v>18610</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="G117" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -4188,20 +4176,20 @@
         <v>117</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C118" s="8"/>
       <c r="D118" s="1">
         <v>18613</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="G118" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -4209,20 +4197,20 @@
         <v>118</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C119" s="8"/>
       <c r="D119" s="1">
         <v>18614</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="G119" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -4230,20 +4218,20 @@
         <v>119</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C120" s="8"/>
       <c r="D120" s="1">
         <v>18620</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G120" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -4251,20 +4239,20 @@
         <v>120</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C121" s="8"/>
       <c r="D121" s="1">
         <v>18621</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="G121" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -4272,20 +4260,20 @@
         <v>121</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C122" s="8"/>
       <c r="D122" s="1">
         <v>18628</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="G122" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -4293,20 +4281,20 @@
         <v>122</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C123" s="8"/>
       <c r="D123" s="1">
         <v>18637</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="G123" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -4314,20 +4302,20 @@
         <v>123</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C124" s="8"/>
       <c r="D124" s="1">
         <v>18638</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="G124" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -4335,20 +4323,20 @@
         <v>124</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C125" s="8"/>
       <c r="D125" s="1">
         <v>18640</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="G125" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -4356,20 +4344,20 @@
         <v>125</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C126" s="8"/>
       <c r="D126" s="1">
         <v>18645</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="G126" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -4377,20 +4365,20 @@
         <v>126</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C127" s="8"/>
       <c r="D127" s="1">
         <v>18649</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="G127" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -4398,20 +4386,20 @@
         <v>127</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C128" s="8"/>
       <c r="D128" s="1">
         <v>18650</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="F128" s="3" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="G128" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -4419,20 +4407,20 @@
         <v>128</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C129" s="8"/>
       <c r="D129" s="1">
         <v>18659</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="F129" s="3" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="G129" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -4440,20 +4428,20 @@
         <v>129</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C130" s="8"/>
       <c r="D130" s="1">
         <v>18670</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="G130" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -4461,20 +4449,20 @@
         <v>130</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C131" s="8"/>
       <c r="D131" s="1">
         <v>18673</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="G131" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -4482,20 +4470,20 @@
         <v>131</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C132" s="8"/>
       <c r="D132" s="1">
         <v>18680</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F132" s="3" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="G132" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -4503,20 +4491,20 @@
         <v>132</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C133" s="8"/>
       <c r="D133" s="1">
         <v>18685</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="F133" s="3" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="G133" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -4524,20 +4512,20 @@
         <v>133</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C134" s="8"/>
       <c r="D134" s="1">
         <v>18686</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="G134" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -4545,20 +4533,20 @@
         <v>134</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C135" s="8"/>
       <c r="D135" s="1">
         <v>18689</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="G135" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -4566,20 +4554,20 @@
         <v>135</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C136" s="8"/>
       <c r="D136" s="1">
         <v>18724</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="G136" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -4587,20 +4575,20 @@
         <v>136</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C137" s="8"/>
       <c r="D137" s="1">
         <v>18780</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="G137" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -4608,20 +4596,20 @@
         <v>137</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C138" s="8"/>
       <c r="D138" s="1">
         <v>18816</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="F138" s="3" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="G138" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -4629,20 +4617,20 @@
         <v>138</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C139" s="8"/>
       <c r="D139" s="1">
         <v>18825</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F139" s="3" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="G139" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -4650,20 +4638,20 @@
         <v>139</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C140" s="8"/>
       <c r="D140" s="1">
         <v>18827</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="F140" s="3" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="G140" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -4671,20 +4659,20 @@
         <v>140</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C141" s="8"/>
       <c r="D141" s="1">
         <v>18840</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="F141" s="3" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G141" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -4692,20 +4680,20 @@
         <v>141</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C142" s="8"/>
       <c r="D142" s="1">
         <v>18847</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F142" s="3" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="G142" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -4713,20 +4701,20 @@
         <v>142</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C143" s="8"/>
       <c r="D143" s="1">
         <v>18848</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="G143" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -4734,20 +4722,20 @@
         <v>143</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C144" s="8"/>
       <c r="D144" s="1">
         <v>18854</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G144" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -4755,20 +4743,20 @@
         <v>144</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C145" s="8"/>
       <c r="D145" s="1">
         <v>18858</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="F145" s="3" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="G145" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -4776,20 +4764,20 @@
         <v>145</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C146" s="8"/>
       <c r="D146" s="1">
         <v>18867</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="F146" s="3" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G146" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -4797,20 +4785,20 @@
         <v>146</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C147" s="8"/>
       <c r="D147" s="1">
         <v>18880</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="F147" s="3" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="G147" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -4818,20 +4806,20 @@
         <v>147</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C148" s="8"/>
       <c r="D148" s="1">
         <v>19904</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="F148" s="3" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="G148" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -4839,20 +4827,20 @@
         <v>148</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C149" s="8"/>
       <c r="D149" s="1">
         <v>18267</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="F149" s="3" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="G149" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -4860,20 +4848,20 @@
         <v>149</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C150" s="8"/>
       <c r="D150" s="1">
         <v>18288</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="F150" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="G150" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -4881,20 +4869,20 @@
         <v>150</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C151" s="8"/>
       <c r="D151" s="1">
         <v>18314</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="F151" s="3" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="G151" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -4902,20 +4890,20 @@
         <v>151</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C152" s="8"/>
       <c r="D152" s="1">
         <v>18545</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="G152" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -4923,20 +4911,20 @@
         <v>152</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C153" s="8"/>
       <c r="D153" s="1">
         <v>18566</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="G153" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -4944,20 +4932,20 @@
         <v>153</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C154" s="8"/>
       <c r="D154" s="1">
         <v>18576</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="G154" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -4965,20 +4953,20 @@
         <v>154</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C155" s="8"/>
       <c r="D155" s="1">
         <v>18603</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="G155" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -4986,20 +4974,20 @@
         <v>155</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C156" s="8"/>
       <c r="D156" s="1">
         <v>18662</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="F156" s="3" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="G156" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -5007,20 +4995,20 @@
         <v>156</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C157" s="8"/>
       <c r="D157" s="1">
         <v>18678</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="G157" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -5028,20 +5016,20 @@
         <v>157</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C158" s="8"/>
       <c r="D158" s="1">
         <v>18691</v>
       </c>
       <c r="E158" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="F158" s="3" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="G158" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -5049,20 +5037,20 @@
         <v>158</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C159" s="8"/>
       <c r="D159" s="1">
         <v>18710</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="F159" s="3" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G159" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -5070,20 +5058,20 @@
         <v>159</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C160" s="8"/>
       <c r="D160" s="1">
         <v>18723</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="G160" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -5091,20 +5079,20 @@
         <v>160</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C161" s="8"/>
       <c r="D161" s="1">
         <v>18730</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="G161" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -5112,20 +5100,20 @@
         <v>161</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C162" s="8"/>
       <c r="D162" s="1">
         <v>18731</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="G162" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -5133,20 +5121,20 @@
         <v>162</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C163" s="8"/>
       <c r="D163" s="1">
         <v>18742</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="G163" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -5154,20 +5142,20 @@
         <v>163</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C164" s="8"/>
       <c r="D164" s="1">
         <v>18758</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="G164" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -5175,20 +5163,20 @@
         <v>164</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C165" s="8"/>
       <c r="D165" s="1">
         <v>18782</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="G165" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -5196,20 +5184,20 @@
         <v>165</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C166" s="8"/>
       <c r="D166" s="1">
         <v>18790</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="F166" s="3" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="G166" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -5217,20 +5205,20 @@
         <v>166</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C167" s="8"/>
       <c r="D167" s="1">
         <v>18795</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="F167" s="3" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="G167" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -5238,20 +5226,20 @@
         <v>167</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C168" s="8"/>
       <c r="D168" s="1">
         <v>18822</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G168" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -5259,20 +5247,20 @@
         <v>168</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C169" s="8"/>
       <c r="D169" s="1">
         <v>18828</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="G169" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -5280,20 +5268,20 @@
         <v>169</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C170" s="8"/>
       <c r="D170" s="1">
         <v>18830</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="F170" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="G170" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -5301,20 +5289,20 @@
         <v>170</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C171" s="8"/>
       <c r="D171" s="1">
         <v>18842</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="G171" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -5322,20 +5310,20 @@
         <v>171</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C172" s="8"/>
       <c r="D172" s="1">
         <v>18846</v>
       </c>
       <c r="E172" s="3" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="F172" s="3" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="G172" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -5343,20 +5331,20 @@
         <v>172</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C173" s="8"/>
       <c r="D173" s="1">
         <v>18857</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="G173" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -5364,20 +5352,20 @@
         <v>173</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C174" s="8"/>
       <c r="D174" s="1">
         <v>18864</v>
       </c>
       <c r="E174" s="3" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="F174" s="3" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="G174" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -5385,20 +5373,20 @@
         <v>174</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C175" s="8"/>
       <c r="D175" s="1">
         <v>18866</v>
       </c>
       <c r="E175" s="3" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="F175" s="3" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="G175" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -5406,20 +5394,20 @@
         <v>175</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C176" s="8"/>
       <c r="D176" s="1">
         <v>18873</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="G176" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -5427,20 +5415,20 @@
         <v>176</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C177" s="8"/>
       <c r="D177" s="1">
         <v>18885</v>
       </c>
       <c r="E177" s="3" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="F177" s="3" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="G177" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -5448,20 +5436,20 @@
         <v>177</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C178" s="8"/>
       <c r="D178" s="1">
         <v>18888</v>
       </c>
       <c r="E178" s="3" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="F178" s="3" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="G178" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -5469,20 +5457,20 @@
         <v>178</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C179" s="8"/>
       <c r="D179" s="1">
         <v>18890</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="G179" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -5490,20 +5478,20 @@
         <v>179</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C180" s="8"/>
       <c r="D180" s="1">
         <v>19916</v>
       </c>
       <c r="E180" s="3" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="F180" s="3" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="G180" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -5511,20 +5499,20 @@
         <v>180</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C181" s="8"/>
       <c r="D181" s="1">
         <v>20310</v>
       </c>
       <c r="E181" s="3" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="F181" s="3" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="G181" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -5532,20 +5520,20 @@
         <v>181</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C182" s="8"/>
       <c r="D182" s="1">
         <v>18619</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="G182" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -5553,20 +5541,20 @@
         <v>182</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C183" s="8"/>
       <c r="D183" s="1">
         <v>18622</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="G183" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -5574,20 +5562,20 @@
         <v>183</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C184" s="8"/>
       <c r="D184" s="1">
         <v>18636</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="G184" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -5595,20 +5583,20 @@
         <v>184</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C185" s="8"/>
       <c r="D185" s="1">
         <v>18643</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="G185" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -5616,20 +5604,20 @@
         <v>185</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C186" s="8"/>
       <c r="D186" s="1">
         <v>18682</v>
       </c>
       <c r="E186" s="3" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="F186" s="3" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="G186" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -5637,20 +5625,20 @@
         <v>186</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C187" s="8"/>
       <c r="D187" s="1">
         <v>18716</v>
       </c>
       <c r="E187" s="3" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="F187" s="3" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="G187" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -5658,20 +5646,20 @@
         <v>187</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C188" s="8"/>
       <c r="D188" s="1">
         <v>18719</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="G188" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -5679,20 +5667,20 @@
         <v>188</v>
       </c>
       <c r="B189" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C189" s="8"/>
       <c r="D189" s="1">
         <v>18727</v>
       </c>
       <c r="E189" s="3" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="F189" s="3" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="G189" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -5700,20 +5688,20 @@
         <v>189</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C190" s="8"/>
       <c r="D190" s="1">
         <v>18738</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="G190" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="191" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -5721,20 +5709,20 @@
         <v>190</v>
       </c>
       <c r="B191" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C191" s="8"/>
       <c r="D191" s="1">
         <v>18741</v>
       </c>
       <c r="E191" s="3" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="F191" s="3" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="G191" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -5742,20 +5730,20 @@
         <v>191</v>
       </c>
       <c r="B192" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C192" s="8"/>
       <c r="D192" s="1">
         <v>18743</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="G192" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="193" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -5763,20 +5751,20 @@
         <v>192</v>
       </c>
       <c r="B193" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C193" s="8"/>
       <c r="D193" s="1">
         <v>18747</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="G193" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="194" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -5784,20 +5772,20 @@
         <v>193</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C194" s="8"/>
       <c r="D194" s="1">
         <v>18751</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="G194" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -5805,20 +5793,20 @@
         <v>194</v>
       </c>
       <c r="B195" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C195" s="8"/>
       <c r="D195" s="1">
         <v>18752</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="G195" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="196" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -5826,20 +5814,20 @@
         <v>195</v>
       </c>
       <c r="B196" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C196" s="8"/>
       <c r="D196" s="1">
         <v>18757</v>
       </c>
       <c r="E196" s="3" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="F196" s="3" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="G196" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -5847,20 +5835,20 @@
         <v>196</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C197" s="8"/>
       <c r="D197" s="1">
         <v>18759</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="G197" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="198" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -5868,20 +5856,20 @@
         <v>197</v>
       </c>
       <c r="B198" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C198" s="8"/>
       <c r="D198" s="1">
         <v>18760</v>
       </c>
       <c r="E198" s="3" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="F198" s="3" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="G198" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -5889,20 +5877,20 @@
         <v>198</v>
       </c>
       <c r="B199" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C199" s="8"/>
       <c r="D199" s="1">
         <v>18766</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="G199" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -5910,20 +5898,20 @@
         <v>199</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C200" s="8"/>
       <c r="D200" s="1">
         <v>18770</v>
       </c>
       <c r="E200" s="3" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="F200" s="3" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="G200" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="201" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -5931,20 +5919,20 @@
         <v>200</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C201" s="8"/>
       <c r="D201" s="1">
         <v>18774</v>
       </c>
       <c r="E201" s="3" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="F201" s="3" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="G201" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="202" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -5952,20 +5940,20 @@
         <v>201</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C202" s="8"/>
       <c r="D202" s="1">
         <v>18797</v>
       </c>
       <c r="E202" s="2" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="G202" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="203" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -5973,20 +5961,20 @@
         <v>202</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C203" s="8"/>
       <c r="D203" s="1">
         <v>18802</v>
       </c>
       <c r="E203" s="2" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="G203" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="204" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -5994,20 +5982,20 @@
         <v>203</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C204" s="8"/>
       <c r="D204" s="1">
         <v>18803</v>
       </c>
       <c r="E204" s="2" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="G204" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="205" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -6015,20 +6003,20 @@
         <v>204</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C205" s="8"/>
       <c r="D205" s="1">
         <v>18808</v>
       </c>
       <c r="E205" s="2" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="G205" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="206" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -6036,20 +6024,20 @@
         <v>205</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C206" s="8"/>
       <c r="D206" s="1">
         <v>18865</v>
       </c>
       <c r="E206" s="3" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="F206" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="G206" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="207" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -6057,20 +6045,20 @@
         <v>206</v>
       </c>
       <c r="B207" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C207" s="8"/>
       <c r="D207" s="1">
         <v>18886</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="G207" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="208" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -6078,20 +6066,20 @@
         <v>207</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C208" s="8"/>
       <c r="D208" s="1">
         <v>19423</v>
       </c>
       <c r="E208" s="2" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="G208" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="209" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -6099,20 +6087,20 @@
         <v>208</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C209" s="8"/>
       <c r="D209" s="1">
         <v>19433</v>
       </c>
       <c r="E209" s="2" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="G209" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="210" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -6120,20 +6108,20 @@
         <v>209</v>
       </c>
       <c r="B210" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C210" s="8"/>
       <c r="D210" s="1">
         <v>18550</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="G210" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="211" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -6141,20 +6129,20 @@
         <v>210</v>
       </c>
       <c r="B211" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C211" s="8"/>
       <c r="D211" s="1">
         <v>18554</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="G211" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="212" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -6162,20 +6150,20 @@
         <v>211</v>
       </c>
       <c r="B212" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C212" s="8"/>
       <c r="D212" s="1">
         <v>18555</v>
       </c>
       <c r="E212" s="2" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="G212" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="213" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -6183,20 +6171,20 @@
         <v>212</v>
       </c>
       <c r="B213" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C213" s="8"/>
       <c r="D213" s="1">
         <v>18560</v>
       </c>
       <c r="E213" s="2" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="G213" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="214" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -6204,20 +6192,20 @@
         <v>213</v>
       </c>
       <c r="B214" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C214" s="8"/>
       <c r="D214" s="1">
         <v>18672</v>
       </c>
       <c r="E214" s="2" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="G214" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="215" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -6225,20 +6213,20 @@
         <v>214</v>
       </c>
       <c r="B215" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C215" s="8"/>
       <c r="D215" s="1">
         <v>18683</v>
       </c>
       <c r="E215" s="2" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="F215" s="2" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="G215" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="216" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -6246,20 +6234,20 @@
         <v>215</v>
       </c>
       <c r="B216" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C216" s="8"/>
       <c r="D216" s="1">
         <v>18702</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="F216" s="2" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="G216" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="217" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -6267,20 +6255,20 @@
         <v>216</v>
       </c>
       <c r="B217" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C217" s="8"/>
       <c r="D217" s="1">
         <v>18814</v>
       </c>
       <c r="E217" s="2" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="F217" s="2" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="G217" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="218" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
@@ -6288,54 +6276,20 @@
         <v>217</v>
       </c>
       <c r="B218" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C218" s="8"/>
       <c r="D218" s="1">
         <v>18913</v>
       </c>
       <c r="E218" s="2" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="F218" s="2" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="G218" s="5" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="219" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
-      <c r="A219" s="4">
-        <v>216</v>
-      </c>
-      <c r="B219" s="1">
-        <v>18814</v>
-      </c>
-      <c r="C219" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D219" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E219" s="5" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="220" spans="1:7" ht="19.5" x14ac:dyDescent="0.45">
-      <c r="A220" s="4">
-        <v>217</v>
-      </c>
-      <c r="B220" s="1">
-        <v>18913</v>
-      </c>
-      <c r="C220" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D220" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E220" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
